--- a/data/processed/cscc_dr_2p5.xlsx
+++ b/data/processed/cscc_dr_2p5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I169"/>
+  <dimension ref="A1:L169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,21 @@
           <t>mean_GtC</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>mean_2020</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>median_GtC</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>median_2020</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -505,7 +520,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.150699125838331</v>
+        <v>1.121718751691772</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.3061459475141298</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.8931469212365873</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.2437628060143524</v>
       </c>
     </row>
     <row r="3">
@@ -538,7 +562,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.064718437098484</v>
+        <v>2.98753345888251</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.8153748523150955</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.842605133787814</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.7758201784355386</v>
       </c>
     </row>
     <row r="4">
@@ -571,7 +604,16 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.06490462231291796</v>
+        <v>0.06326999846013706</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.01726801268016841</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.05531354338288403</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0150964910979487</v>
       </c>
     </row>
     <row r="5">
@@ -604,7 +646,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>8.067633881149339</v>
+        <v>7.86445040503187</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.146411136744506</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7.363350320039585</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.00964801311124</v>
       </c>
     </row>
     <row r="6">
@@ -637,7 +688,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.662327309978054</v>
+        <v>3.570091543645129</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9743699627852427</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.44734952285406</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.9408705029623523</v>
       </c>
     </row>
     <row r="7">
@@ -670,7 +730,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>-0.06305318333880322</v>
+        <v>-0.06146518800339455</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.01677543340703999</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.0616927278166552</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.0168375348844583</v>
       </c>
     </row>
     <row r="8">
@@ -703,7 +772,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.561841638522239</v>
+        <v>3.472136605279979</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.9476355363755401</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.281860593665487</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.8957043104982225</v>
       </c>
     </row>
     <row r="9">
@@ -736,7 +814,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>-0.9032486919482993</v>
+        <v>-0.8805003605623852</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.2403112337779436</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.8572659068020151</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.2339699527298076</v>
       </c>
     </row>
     <row r="10">
@@ -769,7 +856,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.1496518021943073</v>
+        <v>0.1458828193890599</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.03981517996426309</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1167050307831013</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0318518097115451</v>
       </c>
     </row>
     <row r="11">
@@ -802,7 +898,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.6866366588851185</v>
+        <v>0.6693437046884801</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1826811421093014</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.6588391191153594</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1798141700642356</v>
       </c>
     </row>
     <row r="12">
@@ -835,7 +940,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>-0.3946291121530785</v>
+        <v>-0.3846903722492059</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.1049919138234732</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.4010403583703248</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.1094542462801105</v>
       </c>
     </row>
     <row r="13">
@@ -868,7 +982,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.339437350712521</v>
+        <v>1.305703601639543</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.3563601532859016</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.234323329815197</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.3368786380499992</v>
       </c>
     </row>
     <row r="14">
@@ -901,7 +1024,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.337900515499096</v>
+        <v>4.228650428202708</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.154107649618643</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.118017101787951</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.123912964461777</v>
       </c>
     </row>
     <row r="15">
@@ -934,7 +1066,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>10.2303521346216</v>
+        <v>9.972700567973897</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.721806923573662</v>
+      </c>
+      <c r="K15" t="n">
+        <v>9.303332755141746</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.539119201730826</v>
       </c>
     </row>
     <row r="16">
@@ -967,7 +1108,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>-0.1227502970452106</v>
+        <v>-0.1196588290366816</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.03265797735717293</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.1158550779946898</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.03161983569724065</v>
       </c>
     </row>
     <row r="17">
@@ -1000,7 +1150,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.08077050905596581</v>
+        <v>0.07873630261582047</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.02148916556108637</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0749275241607268</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.02044965179059138</v>
       </c>
     </row>
     <row r="18">
@@ -1033,7 +1192,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>-0.06754262930940556</v>
+        <v>-0.06584156721221932</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.01796986004700309</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.06639385277445649</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.01812059300612896</v>
       </c>
     </row>
     <row r="19">
@@ -1066,7 +1234,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>-0.7736052101701465</v>
+        <v>-0.7541219517500751</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.2058193099754572</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.7364312250924342</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.2009910548833063</v>
       </c>
     </row>
     <row r="20">
@@ -1099,7 +1276,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.0472155985314642</v>
+        <v>0.04602647299875931</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.01256181031625527</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.04497117361091494</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.01227379192437635</v>
       </c>
     </row>
     <row r="21">
@@ -1132,7 +1318,16 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.27800303322109</v>
+        <v>1.245816508323714</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.3400154225774328</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.088461816892939</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.2970692731694703</v>
       </c>
     </row>
     <row r="22">
@@ -1165,7 +1360,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>23.45376133500063</v>
+        <v>22.86307801616415</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6.23992303934611</v>
+      </c>
+      <c r="K22" t="n">
+        <v>21.33778105807273</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5.823630201439062</v>
       </c>
     </row>
     <row r="23">
@@ -1198,7 +1402,16 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.2464194498401245</v>
+        <v>0.2402133724277051</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.06556041823900248</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.2308291295084938</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.06299921656891207</v>
       </c>
     </row>
     <row r="24">
@@ -1231,7 +1444,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.1408911138109794</v>
+        <v>0.1373427690695223</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.03748438020456395</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.1209476805903206</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.03300973815238006</v>
       </c>
     </row>
     <row r="25">
@@ -1264,7 +1486,16 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5008811615366352</v>
+        <v>0.4882664622304899</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.133260497333649</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.4678718888939608</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.1276942928204041</v>
       </c>
     </row>
     <row r="26">
@@ -1297,7 +1528,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.3739140382363689</v>
+        <v>0.3644970077690465</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.09948062439111531</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.3519580860573004</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0960584296007916</v>
       </c>
     </row>
     <row r="27">
@@ -1330,7 +1570,16 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>-8.185507817747371</v>
+        <v>-7.979355684829847</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-2.17777174804308</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-7.829640724442383</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-2.136910678068336</v>
       </c>
     </row>
     <row r="28">
@@ -1363,7 +1612,16 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>-1.101344328567296</v>
+        <v>-1.073606955704673</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-0.2930149988276947</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-1.050648891091317</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-0.2867491514987219</v>
       </c>
     </row>
     <row r="29">
@@ -1396,7 +1654,16 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>-0.5414225202309575</v>
+        <v>-0.5277867862190498</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-0.1440466119593476</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-0.5154150450455871</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-0.140670045045193</v>
       </c>
     </row>
     <row r="30">
@@ -1429,7 +1696,16 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>61.19593243190997</v>
+        <v>59.65471198748471</v>
+      </c>
+      <c r="J30" t="n">
+        <v>16.28130785684626</v>
+      </c>
+      <c r="K30" t="n">
+        <v>54.07124489355239</v>
+      </c>
+      <c r="L30" t="n">
+        <v>14.75743583339312</v>
       </c>
     </row>
     <row r="31">
@@ -1462,7 +1738,16 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.894600792984135</v>
+        <v>2.821700230098513</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.7701146916207734</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.691316630808618</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.7345296481464568</v>
       </c>
     </row>
     <row r="32">
@@ -1495,7 +1780,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>8.40982895013919</v>
+        <v>8.198027286254169</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.237452861968932</v>
+      </c>
+      <c r="K32" t="n">
+        <v>8.039145889023391</v>
+      </c>
+      <c r="L32" t="n">
+        <v>2.194090035213808</v>
       </c>
     </row>
     <row r="33">
@@ -1528,7 +1822,16 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.075457152934838</v>
+        <v>1.04837174896537</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.2861276607438238</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.019946656845045</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.278369720754652</v>
       </c>
     </row>
     <row r="34">
@@ -1561,7 +1864,16 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.321602986935155</v>
+        <v>6.162393324171298</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.681875907251992</v>
+      </c>
+      <c r="K34" t="n">
+        <v>5.848718456826736</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.596265954374109</v>
       </c>
     </row>
     <row r="35">
@@ -1594,7 +1906,16 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.06036590860580737</v>
+        <v>0.0588455923234614</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.01606047825421981</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.05566357763502276</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.01519202446370709</v>
       </c>
     </row>
     <row r="36">
@@ -1627,7 +1948,16 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.02662861626626027</v>
+        <v>0.02595797418000757</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.007084599939958399</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.0248751492631675</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.006789069122043532</v>
       </c>
     </row>
     <row r="37">
@@ -1660,7 +1990,16 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7174651943990056</v>
+        <v>0.6993958230890475</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.1908831394893689</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.6486635764218317</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.1770370022985348</v>
       </c>
     </row>
     <row r="38">
@@ -1693,7 +2032,16 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.637643770982474</v>
+        <v>0.6215847033770893</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.1696464801793366</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.5756834653689237</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.1571188497185927</v>
       </c>
     </row>
     <row r="39">
@@ -1726,7 +2074,16 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.1234447257542561</v>
+        <v>0.1203357685486344</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.03284273159078449</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.1083467516936288</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.02957062000371966</v>
       </c>
     </row>
     <row r="40">
@@ -1759,7 +2116,16 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>-1.186672828718042</v>
+        <v>-1.156786456343552</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-0.3157168276046813</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-1.130452303525845</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-0.308529558822556</v>
       </c>
     </row>
     <row r="41">
@@ -1792,7 +2158,16 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>-4.767786034695486</v>
+        <v>-4.647709274373319</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-1.268479605451234</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-4.656339862838609</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-1.270835115403551</v>
       </c>
     </row>
     <row r="42">
@@ -1825,7 +2200,16 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.1622546248939291</v>
+        <v>0.1581682398165007</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.04316818772284407</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.1519918397350536</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.04148248901065874</v>
       </c>
     </row>
     <row r="43">
@@ -1858,7 +2242,16 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>-0.5715866243502472</v>
+        <v>-0.5571912069393139</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-0.1520718359550529</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-0.5498591076977375</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-0.1500707171664131</v>
       </c>
     </row>
     <row r="44">
@@ -1891,7 +2284,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.453930117831889</v>
+        <v>1.417312866761135</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.3868211972601352</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1.382555707243639</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.3773350729376744</v>
       </c>
     </row>
     <row r="45">
@@ -1924,7 +2326,16 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.857625967095462</v>
+        <v>2.785656615735248</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.7602774606264324</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2.630853157252324</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.7180276084203941</v>
       </c>
     </row>
     <row r="46">
@@ -1957,7 +2368,16 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.508956939396733</v>
+        <v>1.470953837028071</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.4014612000622464</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1.356021789686422</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.3700932832113598</v>
       </c>
     </row>
     <row r="47">
@@ -1990,7 +2410,16 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>15.24385695590725</v>
+        <v>14.85994019773907</v>
+      </c>
+      <c r="J47" t="n">
+        <v>4.055660534317431</v>
+      </c>
+      <c r="K47" t="n">
+        <v>14.04114025607576</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3.832188934518494</v>
       </c>
     </row>
     <row r="48">
@@ -2023,7 +2452,16 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.2655853007795487</v>
+        <v>0.258896531133695</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.07065953360635781</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.2514602601672494</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.06862998367010081</v>
       </c>
     </row>
     <row r="49">
@@ -2056,7 +2494,16 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.094507967548864</v>
+        <v>3.016572739577139</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.8233004201902672</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2.651542136360098</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.7236741638537385</v>
       </c>
     </row>
     <row r="50">
@@ -2089,7 +2536,16 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>-0.2120882078162924</v>
+        <v>-0.2067467632313654</v>
+      </c>
+      <c r="J50" t="n">
+        <v>-0.05642651834917177</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-0.2038280523377194</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-0.05562992694806754</v>
       </c>
     </row>
     <row r="51">
@@ -2122,7 +2578,16 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7.893951072050955</v>
+        <v>7.695141799995586</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.100202456330673</v>
+      </c>
+      <c r="K51" t="n">
+        <v>7.058222485836649</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1.926370765785112</v>
       </c>
     </row>
     <row r="52">
@@ -2155,7 +2620,16 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>-1.78488024829493</v>
+        <v>-1.73992801339625</v>
+      </c>
+      <c r="J52" t="n">
+        <v>-0.4748711826954831</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-1.718691390371083</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-0.469075161127479</v>
       </c>
     </row>
     <row r="53">
@@ -2188,7 +2662,16 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.05262356936768738</v>
+        <v>0.05129824401116386</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.01400061244846175</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.04771929923419551</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.0130238262102062</v>
       </c>
     </row>
     <row r="54">
@@ -2221,7 +2704,16 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>-0.4070248236206286</v>
+        <v>-0.3967738975439538</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-0.1082898191986774</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-0.5403967054153639</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-0.1474881837924028</v>
       </c>
     </row>
     <row r="55">
@@ -2254,7 +2746,16 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.400086040265959</v>
+        <v>0.3900098675485463</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.1064437411431622</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.3757753400804724</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.1025587718560241</v>
       </c>
     </row>
     <row r="56">
@@ -2287,7 +2788,16 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>-3.373843129007983</v>
+        <v>-3.28887284095009</v>
+      </c>
+      <c r="J56" t="n">
+        <v>-0.8976181334470769</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-3.29871568010639</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-0.9003044978456305</v>
       </c>
     </row>
     <row r="57">
@@ -2320,7 +2830,16 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.000199058234873329</v>
+        <v>0.0001940449503456468</v>
+      </c>
+      <c r="J57" t="n">
+        <v>5.295986636071147e-05</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-0.006056005909597471</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-0.001652840040829004</v>
       </c>
     </row>
     <row r="58">
@@ -2353,7 +2872,16 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.442093907558487</v>
+        <v>4.330219708174344</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.181828522973347</v>
+      </c>
+      <c r="K58" t="n">
+        <v>4.127925959212479</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1.126617346946637</v>
       </c>
     </row>
     <row r="59">
@@ -2386,7 +2914,16 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.137633924636648</v>
+        <v>2.083797583291368</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.5687220478415307</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1.99545507901143</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.544611102350281</v>
       </c>
     </row>
     <row r="60">
@@ -2419,7 +2956,16 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.2580027285645905</v>
+        <v>0.2515049261097675</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.06864217415659593</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.2476834354055343</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.06759919088578993</v>
       </c>
     </row>
     <row r="61">
@@ -2452,7 +2998,16 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.2154560774817583</v>
+        <v>0.2100298130505392</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.05732254722995066</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.2040143238698545</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.05568076524832272</v>
       </c>
     </row>
     <row r="62">
@@ -2485,7 +3040,16 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.3461933789030712</v>
+        <v>0.3374744936424579</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.0921054840727232</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.3207200407018551</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.08753276220028795</v>
       </c>
     </row>
     <row r="63">
@@ -2518,7 +3082,16 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8579891040151122</v>
+        <v>0.8363806360066621</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.2282698242376261</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.7151305717717316</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.1951775577979617</v>
       </c>
     </row>
     <row r="64">
@@ -2551,7 +3124,16 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.268043659354123</v>
+        <v>2.210922946951628</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.6034178348667106</v>
+      </c>
+      <c r="K64" t="n">
+        <v>2.159879304307819</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.5894867096909985</v>
       </c>
     </row>
     <row r="65">
@@ -2584,7 +3166,16 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.06152125958987534</v>
+        <v>0.05997184577626594</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.01636786183850053</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.05753442675515408</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.01570262738950712</v>
       </c>
     </row>
     <row r="66">
@@ -2617,7 +3208,16 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.106567452723376</v>
+        <v>1.078698535403251</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.2944046221078743</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1.063125941179711</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.2901544599289604</v>
       </c>
     </row>
     <row r="67">
@@ -2650,7 +3250,16 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.01924047286681849</v>
+        <v>0.01875590127906232</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.005118968689700414</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.0161582401584589</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.004410000043247516</v>
       </c>
     </row>
     <row r="68">
@@ -2683,7 +3292,16 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7192828679928236</v>
+        <v>0.7011677185470849</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.1913667354113223</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.6704878666894611</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.1829934133977787</v>
       </c>
     </row>
     <row r="69">
@@ -2716,7 +3334,16 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>-0.1253785485537475</v>
+        <v>-0.1222208879929185</v>
+      </c>
+      <c r="J69" t="n">
+        <v>-0.03335722925570919</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-0.140160395371527</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-0.03825338301624644</v>
       </c>
     </row>
     <row r="70">
@@ -2749,7 +3376,16 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>30.79893538082093</v>
+        <v>30.02326374728108</v>
+      </c>
+      <c r="J70" t="n">
+        <v>8.194122201768854</v>
+      </c>
+      <c r="K70" t="n">
+        <v>28.48048819212377</v>
+      </c>
+      <c r="L70" t="n">
+        <v>7.773059004400591</v>
       </c>
     </row>
     <row r="71">
@@ -2782,7 +3418,16 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>200.6955864405566</v>
+        <v>195.6410651899447</v>
+      </c>
+      <c r="J71" t="n">
+        <v>53.39548722432987</v>
+      </c>
+      <c r="K71" t="n">
+        <v>186.1094843540949</v>
+      </c>
+      <c r="L71" t="n">
+        <v>50.79407324074644</v>
       </c>
     </row>
     <row r="72">
@@ -2815,7 +3460,16 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>-0.4132353288420759</v>
+        <v>-0.4028279911014698</v>
+      </c>
+      <c r="J72" t="n">
+        <v>-0.1099421373093531</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-0.407441563245542</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-0.1112013000124296</v>
       </c>
     </row>
     <row r="73">
@@ -2848,7 +3502,16 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.482721601515428</v>
+        <v>5.344639178590513</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1.458689732148066</v>
+      </c>
+      <c r="K73" t="n">
+        <v>4.802128015886639</v>
+      </c>
+      <c r="L73" t="n">
+        <v>1.310624458484345</v>
       </c>
     </row>
     <row r="74">
@@ -2881,7 +3544,16 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.044529682000781</v>
+        <v>5.892298114433764</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1.608159965729739</v>
+      </c>
+      <c r="K74" t="n">
+        <v>5.651823399504845</v>
+      </c>
+      <c r="L74" t="n">
+        <v>1.542528220388877</v>
       </c>
     </row>
     <row r="75">
@@ -2914,7 +3586,16 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>-0.1677661708121427</v>
+        <v>-0.163540977370956</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-0.04463454622569758</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-0.1613255141458444</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.04402988923194443</v>
       </c>
     </row>
     <row r="76">
@@ -2947,7 +3628,16 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.348582752716972</v>
+        <v>3.264248647601742</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.890897556659864</v>
+      </c>
+      <c r="K76" t="n">
+        <v>3.0863466668367</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.8423435226082696</v>
       </c>
     </row>
     <row r="77">
@@ -2980,7 +3670,16 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.08190976346993</v>
+        <v>2.02947683593053</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.5538965163565855</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1.885902032357542</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.5147112533726915</v>
       </c>
     </row>
     <row r="78">
@@ -3013,7 +3712,16 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.1386514243473583</v>
+        <v>0.1351594862174737</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.03688850606372098</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.1273422401002041</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.03475497819328714</v>
       </c>
     </row>
     <row r="79">
@@ -3046,7 +3754,16 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.153061829873526</v>
+        <v>1.124021950991628</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.3067745499431298</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1.056075827864658</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.2882303023648083</v>
       </c>
     </row>
     <row r="80">
@@ -3079,7 +3796,16 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>5.266963300192281</v>
+        <v>5.134314753210407</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1.401286777622928</v>
+      </c>
+      <c r="K80" t="n">
+        <v>4.508821142555242</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1.230573455937566</v>
       </c>
     </row>
     <row r="81">
@@ -3112,7 +3838,16 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>-1.896572224223629</v>
+        <v>-1.848807025293865</v>
+      </c>
+      <c r="J81" t="n">
+        <v>-0.5045870702221248</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-1.82387648413448</v>
+      </c>
+      <c r="L81" t="n">
+        <v>-0.4977828832244761</v>
       </c>
     </row>
     <row r="82">
@@ -3145,7 +3880,16 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.725503589144995</v>
+        <v>3.631676727306447</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.9911781460989211</v>
+      </c>
+      <c r="K82" t="n">
+        <v>3.318003324892036</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.9055685930382196</v>
       </c>
     </row>
     <row r="83">
@@ -3178,7 +3922,16 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>-0.1929754740939682</v>
+        <v>-0.1881153839845936</v>
+      </c>
+      <c r="J83" t="n">
+        <v>-0.05134153493029301</v>
+      </c>
+      <c r="K83" t="n">
+        <v>-0.1871198713782328</v>
+      </c>
+      <c r="L83" t="n">
+        <v>-0.05106983389143908</v>
       </c>
     </row>
     <row r="84">
@@ -3211,7 +3964,16 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.64410268405592</v>
+        <v>1.602695934151083</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.4374170125958195</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1.556427424389464</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.4247891442110981</v>
       </c>
     </row>
     <row r="85">
@@ -3244,7 +4006,16 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>-1.00052426444597</v>
+        <v>-0.9753260463581347</v>
+      </c>
+      <c r="J85" t="n">
+        <v>-0.2661916065387922</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-1.09323958679715</v>
+      </c>
+      <c r="L85" t="n">
+        <v>-0.2983732496717112</v>
       </c>
     </row>
     <row r="86">
@@ -3277,7 +4048,16 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.317612791418929</v>
+        <v>3.234058665227441</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.8826579326494106</v>
+      </c>
+      <c r="K86" t="n">
+        <v>3.102973948666395</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.8468815362080772</v>
       </c>
     </row>
     <row r="87">
@@ -3310,7 +4090,16 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7500719072435792</v>
+        <v>0.7311813353984797</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.1995582247266593</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.6891909825339347</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.1880979755824057</v>
       </c>
     </row>
     <row r="88">
@@ -3343,7 +4132,16 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.1865293830375439</v>
+        <v>0.1818316378247659</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.04962653870763261</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.1634573624531603</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.04461172556036035</v>
       </c>
     </row>
     <row r="89">
@@ -3376,7 +4174,16 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7097619867581108</v>
+        <v>0.6918866208441323</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.1888336847282021</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0.6606013765793991</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.180295135529312</v>
       </c>
     </row>
     <row r="90">
@@ -3409,7 +4216,16 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.545453448131762</v>
+        <v>1.506531180662133</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.4111711737614991</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1.441445035434004</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.3934074878367915</v>
       </c>
     </row>
     <row r="91">
@@ -3442,7 +4258,16 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.052533632867978</v>
+        <v>2.975655529122987</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.8121330592584571</v>
+      </c>
+      <c r="K91" t="n">
+        <v>2.848781140684896</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.7775057698375808</v>
       </c>
     </row>
     <row r="92">
@@ -3475,7 +4300,16 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.01854432011416879</v>
+        <v>0.01807728114356851</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.004933755770624593</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.01376996035338997</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.003758176952344423</v>
       </c>
     </row>
     <row r="93">
@@ -3508,7 +4342,16 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>-0.2350874518367907</v>
+        <v>-0.2291667709581745</v>
+      </c>
+      <c r="J93" t="n">
+        <v>-0.06254551609120483</v>
+      </c>
+      <c r="K93" t="n">
+        <v>-0.2257204482463167</v>
+      </c>
+      <c r="L93" t="n">
+        <v>-0.0616049258314183</v>
       </c>
     </row>
     <row r="94">
@@ -3541,7 +4384,16 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>-0.07021877742929379</v>
+        <v>-0.06845031650295709</v>
+      </c>
+      <c r="J94" t="n">
+        <v>-0.0186818549407634</v>
+      </c>
+      <c r="K94" t="n">
+        <v>-0.06801532939686609</v>
+      </c>
+      <c r="L94" t="n">
+        <v>-0.01856313575241978</v>
       </c>
     </row>
     <row r="95">
@@ -3574,7 +4426,16 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>-0.1718398883618921</v>
+        <v>-0.1675120982852268</v>
+      </c>
+      <c r="J95" t="n">
+        <v>-0.04571836743592435</v>
+      </c>
+      <c r="K95" t="n">
+        <v>-0.1657812213656211</v>
+      </c>
+      <c r="L95" t="n">
+        <v>-0.04524596652991841</v>
       </c>
     </row>
     <row r="96">
@@ -3607,7 +4468,16 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.543058894409878</v>
+        <v>2.479011919330236</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.6765862225246276</v>
+      </c>
+      <c r="K96" t="n">
+        <v>2.295869292559299</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.6266018811570139</v>
       </c>
     </row>
     <row r="97">
@@ -3640,7 +4510,16 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>-0.03071355182107647</v>
+        <v>-0.02994003057372516</v>
+      </c>
+      <c r="J97" t="n">
+        <v>-0.008171405724269968</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-0.03177965542577638</v>
+      </c>
+      <c r="L97" t="n">
+        <v>-0.008673486742842898</v>
       </c>
     </row>
     <row r="98">
@@ -3673,7 +4552,16 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.681345233700306</v>
+        <v>1.639000529643396</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.4473254720642457</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1.543144101421279</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.4211637831389954</v>
       </c>
     </row>
     <row r="99">
@@ -3706,7 +4594,16 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>16.06626419342724</v>
+        <v>15.66163509707352</v>
+      </c>
+      <c r="J99" t="n">
+        <v>4.274463727367226</v>
+      </c>
+      <c r="K99" t="n">
+        <v>14.65748601931956</v>
+      </c>
+      <c r="L99" t="n">
+        <v>4.000405572958395</v>
       </c>
     </row>
     <row r="100">
@@ -3739,7 +4636,16 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>-0.04176683093014531</v>
+        <v>-0.04071493268837872</v>
+      </c>
+      <c r="J100" t="n">
+        <v>-0.01111215411800729</v>
+      </c>
+      <c r="K100" t="n">
+        <v>-0.04332876959915425</v>
+      </c>
+      <c r="L100" t="n">
+        <v>-0.01182553755435433</v>
       </c>
     </row>
     <row r="101">
@@ -3772,7 +4678,16 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.135273856583627</v>
+        <v>3.056311939106265</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0.8341462715901378</v>
+      </c>
+      <c r="K101" t="n">
+        <v>2.982126844764827</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.8138992480253346</v>
       </c>
     </row>
     <row r="102">
@@ -3805,7 +4720,16 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.693384817153874</v>
+        <v>1.650736896013351</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.4505286288246045</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1.551314001837371</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0.4233935594534308</v>
       </c>
     </row>
     <row r="103">
@@ -3838,7 +4762,16 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>-0.0210347472021311</v>
+        <v>-0.02050498678925868</v>
+      </c>
+      <c r="J103" t="n">
+        <v>-0.005596339189208156</v>
+      </c>
+      <c r="K103" t="n">
+        <v>-0.01991992604979346</v>
+      </c>
+      <c r="L103" t="n">
+        <v>-0.00543666103979079</v>
       </c>
     </row>
     <row r="104">
@@ -3871,7 +4804,16 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>-0.9522606384178791</v>
+        <v>-0.9282779404504274</v>
+      </c>
+      <c r="J104" t="n">
+        <v>-0.2533509662801385</v>
+      </c>
+      <c r="K104" t="n">
+        <v>-0.8880174052899868</v>
+      </c>
+      <c r="L104" t="n">
+        <v>-0.2423628289546907</v>
       </c>
     </row>
     <row r="105">
@@ -3904,7 +4846,16 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.187977004511492</v>
+        <v>3.107687757490416</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.8481680560836288</v>
+      </c>
+      <c r="K105" t="n">
+        <v>2.981878893202782</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0.8138315756557811</v>
       </c>
     </row>
     <row r="106">
@@ -3937,7 +4888,16 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.7212703122476727</v>
+        <v>0.7031051089895972</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0.1918954991783835</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0.6881391169075223</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0.1878108943524897</v>
       </c>
     </row>
     <row r="107">
@@ -3970,7 +4930,16 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.2025007378581915</v>
+        <v>0.1974007538429876</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.05387575159470184</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0.1890025952169686</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.0515836777338888</v>
       </c>
     </row>
     <row r="108">
@@ -4003,7 +4972,16 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.833740046672035</v>
+        <v>2.762372262563558</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.753922560743329</v>
+      </c>
+      <c r="K108" t="n">
+        <v>2.689525458665899</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.7340407911206056</v>
       </c>
     </row>
     <row r="109">
@@ -4036,7 +5014,16 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>8.717803690388925</v>
+        <v>8.498245678211187</v>
+      </c>
+      <c r="J109" t="n">
+        <v>2.319390196018337</v>
+      </c>
+      <c r="K109" t="n">
+        <v>8.140367988328745</v>
+      </c>
+      <c r="L109" t="n">
+        <v>2.221716154019854</v>
       </c>
     </row>
     <row r="110">
@@ -4069,7 +5056,16 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.3680812734052412</v>
+        <v>0.3588111412046501</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0.0979288049139329</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0.3411309496219239</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0.0931034251151539</v>
       </c>
     </row>
     <row r="111">
@@ -4102,7 +5098,16 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.04040589686948526</v>
+        <v>0.03938827377174296</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0.01075007471936216</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0.03776650642088206</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0.01030745262578659</v>
       </c>
     </row>
     <row r="112">
@@ -4135,7 +5140,16 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>5.129985875679571</v>
+        <v>5.000787107117505</v>
+      </c>
+      <c r="J112" t="n">
+        <v>1.364843642772245</v>
+      </c>
+      <c r="K112" t="n">
+        <v>4.770546255613048</v>
+      </c>
+      <c r="L112" t="n">
+        <v>1.302004982427142</v>
       </c>
     </row>
     <row r="113">
@@ -4168,7 +5182,16 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>54.26672364156068</v>
+        <v>52.9000154208565</v>
+      </c>
+      <c r="J113" t="n">
+        <v>14.43777713451324</v>
+      </c>
+      <c r="K113" t="n">
+        <v>50.0671695627823</v>
+      </c>
+      <c r="L113" t="n">
+        <v>13.6646205138598</v>
       </c>
     </row>
     <row r="114">
@@ -4201,7 +5224,16 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.680518383505642</v>
+        <v>0.6633795181630294</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0.1810533619440582</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0.652718300829117</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0.1781436410559817</v>
       </c>
     </row>
     <row r="115">
@@ -4234,7 +5266,16 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>-1.1423041819264</v>
+        <v>-1.113535234563823</v>
+      </c>
+      <c r="J115" t="n">
+        <v>-0.303912454848205</v>
+      </c>
+      <c r="K115" t="n">
+        <v>-1.095475247569395</v>
+      </c>
+      <c r="L115" t="n">
+        <v>-0.2989834190964505</v>
       </c>
     </row>
     <row r="116">
@@ -4267,7 +5308,16 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>-1.576773965263655</v>
+        <v>-1.537062890116532</v>
+      </c>
+      <c r="J116" t="n">
+        <v>-0.4195040638964334</v>
+      </c>
+      <c r="K116" t="n">
+        <v>-1.535539984377199</v>
+      </c>
+      <c r="L116" t="n">
+        <v>-0.4190884236837334</v>
       </c>
     </row>
     <row r="117">
@@ -4300,7 +5350,16 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.217689352639317</v>
+        <v>2.161836814180573</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.5900209645689337</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1.981699426355767</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.5408568303372726</v>
       </c>
     </row>
     <row r="118">
@@ -4333,7 +5392,16 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.03964083923807789</v>
+        <v>0.03864248412786075</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.01054652951087902</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.01770132525962957</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.004831147723698027</v>
       </c>
     </row>
     <row r="119">
@@ -4366,7 +5434,16 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.723997159174478</v>
+        <v>1.680578265756894</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.4586731074664011</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1.601163901150787</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.4369988813184463</v>
       </c>
     </row>
     <row r="120">
@@ -4399,7 +5476,16 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>26.50493449118464</v>
+        <v>25.83740733222815</v>
+      </c>
+      <c r="J120" t="n">
+        <v>7.051694140891963</v>
+      </c>
+      <c r="K120" t="n">
+        <v>24.55977817230573</v>
+      </c>
+      <c r="L120" t="n">
+        <v>6.702996226065976</v>
       </c>
     </row>
     <row r="121">
@@ -4432,7 +5518,16 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.097782869654614</v>
+        <v>1.070135192186278</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.2920674651163423</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.9903654197234983</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.270296239007505</v>
       </c>
     </row>
     <row r="122">
@@ -4465,7 +5560,16 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.289891052569481</v>
+        <v>2.232220113252503</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.609230380254504</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1.952792145294524</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.5329672885629159</v>
       </c>
     </row>
     <row r="123">
@@ -4498,7 +5602,16 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>11.99621655114178</v>
+        <v>11.694091663594</v>
+      </c>
+      <c r="J123" t="n">
+        <v>3.191618903819323</v>
+      </c>
+      <c r="K123" t="n">
+        <v>11.02677190442262</v>
+      </c>
+      <c r="L123" t="n">
+        <v>3.00949014858696</v>
       </c>
     </row>
     <row r="124">
@@ -4531,7 +5644,16 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7670801108432977</v>
+        <v>0.7477611871442577</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.2040832934345681</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.7076378528463909</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.1931326017593862</v>
       </c>
     </row>
     <row r="125">
@@ -4564,7 +5686,16 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>-2.105149305923407</v>
+        <v>-2.052131090170803</v>
+      </c>
+      <c r="J125" t="n">
+        <v>-0.5600794460073153</v>
+      </c>
+      <c r="K125" t="n">
+        <v>-2.039993139893524</v>
+      </c>
+      <c r="L125" t="n">
+        <v>-0.5567666866521626</v>
       </c>
     </row>
     <row r="126">
@@ -4597,7 +5728,16 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.5706325288754195</v>
+        <v>0.5562611403728351</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.1518179968266471</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.500340301852981</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.1365557592393507</v>
       </c>
     </row>
     <row r="127">
@@ -4630,7 +5770,16 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.125512115965269</v>
+        <v>1.097166077027075</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.2994448900183066</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1.091949578453586</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.2980211731587297</v>
       </c>
     </row>
     <row r="128">
@@ -4663,7 +5812,16 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.179374283328061</v>
+        <v>3.099301695964559</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.8458792838331221</v>
+      </c>
+      <c r="K128" t="n">
+        <v>2.937631601391928</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.8017553497248712</v>
       </c>
     </row>
     <row r="129">
@@ -4696,7 +5854,16 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>-0.4417802651596588</v>
+        <v>-0.4306540227845587</v>
+      </c>
+      <c r="J129" t="n">
+        <v>-0.1175365782708949</v>
+      </c>
+      <c r="K129" t="n">
+        <v>-0.443534882168684</v>
+      </c>
+      <c r="L129" t="n">
+        <v>-0.1210520966617587</v>
       </c>
     </row>
     <row r="130">
@@ -4729,7 +5896,16 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>-22.83310283291796</v>
+        <v>-22.25805080744367</v>
+      </c>
+      <c r="J130" t="n">
+        <v>-6.074795526049037</v>
+      </c>
+      <c r="K130" t="n">
+        <v>-21.86396056040442</v>
+      </c>
+      <c r="L130" t="n">
+        <v>-5.96723814421518</v>
       </c>
     </row>
     <row r="131">
@@ -4762,7 +5938,16 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.178310572880693</v>
+        <v>1.148634804040554</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3134920316704568</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1.124653053215584</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.3069467939998864</v>
       </c>
     </row>
     <row r="132">
@@ -4795,7 +5980,16 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>16.29338340339163</v>
+        <v>15.88303430644623</v>
+      </c>
+      <c r="J132" t="n">
+        <v>4.334889275776809</v>
+      </c>
+      <c r="K132" t="n">
+        <v>15.42804193155908</v>
+      </c>
+      <c r="L132" t="n">
+        <v>4.210710134159139</v>
       </c>
     </row>
     <row r="133">
@@ -4828,7 +6022,16 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>11.40271200258139</v>
+        <v>11.11553453568315</v>
+      </c>
+      <c r="J133" t="n">
+        <v>3.033715757555445</v>
+      </c>
+      <c r="K133" t="n">
+        <v>10.76214436207021</v>
+      </c>
+      <c r="L133" t="n">
+        <v>2.937266474364139</v>
       </c>
     </row>
     <row r="134">
@@ -4861,7 +6064,16 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.10007372777078</v>
+        <v>2.047183340527445</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.5587290776548702</v>
+      </c>
+      <c r="K134" t="n">
+        <v>2.025391516057831</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.5527815273083601</v>
       </c>
     </row>
     <row r="135">
@@ -4894,7 +6106,16 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.07126034842101588</v>
+        <v>0.06946565551417051</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.01895896711631291</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.06711844551407753</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.0183183530333181</v>
       </c>
     </row>
     <row r="136">
@@ -4927,7 +6148,16 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.7027805813514566</v>
+        <v>0.6850810422337368</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.1869762669851902</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.6571203473065322</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.1793450729548396</v>
       </c>
     </row>
     <row r="137">
@@ -4960,7 +6190,16 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.4670889114084369</v>
+        <v>0.4553252704110878</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.1242699973829388</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.4434839512119437</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.1210381962914693</v>
       </c>
     </row>
     <row r="138">
@@ -4993,7 +6232,16 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.100910885242911</v>
+        <v>0.09836944313686136</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.02684755544128312</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.09111243970241094</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.02486693223319076</v>
       </c>
     </row>
     <row r="139">
@@ -5026,7 +6274,16 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>-0.140711219099843</v>
+        <v>-0.1371674050092909</v>
+      </c>
+      <c r="J139" t="n">
+        <v>-0.03743651883441345</v>
+      </c>
+      <c r="K139" t="n">
+        <v>-0.1399150146838811</v>
+      </c>
+      <c r="L139" t="n">
+        <v>-0.03818641230455271</v>
       </c>
     </row>
     <row r="140">
@@ -5059,7 +6316,16 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.02557701754465654</v>
+        <v>0.02493285998743476</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.006804819865566254</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.02442248503969139</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.006665525392928874</v>
       </c>
     </row>
     <row r="141">
@@ -5092,7 +6358,16 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.1075011063006614</v>
+        <v>0.1047936893818448</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.0286008977570537</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.100882020650006</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.02753330257915011</v>
       </c>
     </row>
     <row r="142">
@@ -5125,7 +6400,16 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>-0.3967608540359397</v>
+        <v>-0.3867684261818793</v>
+      </c>
+      <c r="J142" t="n">
+        <v>-0.1055590682810806</v>
+      </c>
+      <c r="K142" t="n">
+        <v>-0.382705874866249</v>
+      </c>
+      <c r="L142" t="n">
+        <v>-0.1044502933586924</v>
       </c>
     </row>
     <row r="143">
@@ -5158,7 +6442,16 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>-0.1478062264147738</v>
+        <v>-0.1440837244622581</v>
+      </c>
+      <c r="J143" t="n">
+        <v>-0.0393241606065115</v>
+      </c>
+      <c r="K143" t="n">
+        <v>-0.1408758632525414</v>
+      </c>
+      <c r="L143" t="n">
+        <v>-0.03844865263442724</v>
       </c>
     </row>
     <row r="144">
@@ -5191,7 +6484,16 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>-2.334846665777574</v>
+        <v>-2.276043518690986</v>
+      </c>
+      <c r="J144" t="n">
+        <v>-0.621190916673304</v>
+      </c>
+      <c r="K144" t="n">
+        <v>-2.245897826817714</v>
+      </c>
+      <c r="L144" t="n">
+        <v>-0.6129633806816905</v>
       </c>
     </row>
     <row r="145">
@@ -5224,7 +6526,16 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.09854281418829389</v>
+        <v>0.09606101198604484</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0.02621752510536158</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0.09179199750487846</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0.02505240106574194</v>
       </c>
     </row>
     <row r="146">
@@ -5257,7 +6568,16 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.877475277170485</v>
+        <v>2.805006020648611</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0.765558411749075</v>
+      </c>
+      <c r="K146" t="n">
+        <v>2.67660139061804</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0.7305134799721724</v>
       </c>
     </row>
     <row r="147">
@@ -5290,7 +6610,16 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.585439431986264</v>
+        <v>2.520325102454083</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0.6878616545999134</v>
+      </c>
+      <c r="K147" t="n">
+        <v>2.438431839050882</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0.6655108731034065</v>
       </c>
     </row>
     <row r="148">
@@ -5323,7 +6652,16 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.6727949538935287</v>
+        <v>0.6558506032375339</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0.1789985270844797</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0.6214857364855439</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0.1696194695648318</v>
       </c>
     </row>
     <row r="149">
@@ -5356,7 +6694,16 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>13.8298709847905</v>
+        <v>13.48156548377964</v>
+      </c>
+      <c r="J149" t="n">
+        <v>3.679466562166934</v>
+      </c>
+      <c r="K149" t="n">
+        <v>12.75746623836612</v>
+      </c>
+      <c r="L149" t="n">
+        <v>3.481841222261494</v>
       </c>
     </row>
     <row r="150">
@@ -5389,7 +6736,16 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.09500651214797716</v>
+        <v>0.09261377176381975</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0.02527668443335692</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0.07301879046043408</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0.01992870918679969</v>
       </c>
     </row>
     <row r="151">
@@ -5422,7 +6778,16 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.5463541318871892</v>
+        <v>0.5325941951643087</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0.1453586777195166</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0.5065583550464146</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0.1382528261589559</v>
       </c>
     </row>
     <row r="152">
@@ -5455,7 +6820,16 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.2163196944911928</v>
+        <v>0.2108716798530858</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0.05755231437038367</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0.2002149258806802</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0.05464381164865725</v>
       </c>
     </row>
     <row r="153">
@@ -5488,7 +6862,16 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.367960018808822</v>
+        <v>1.333507925926826</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0.3639486697398542</v>
+      </c>
+      <c r="K153" t="n">
+        <v>1.27275318298226</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0.3473671350934116</v>
       </c>
     </row>
     <row r="154">
@@ -5521,7 +6904,16 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.373558444545717</v>
+        <v>2.3137803407503</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0.631490267672025</v>
+      </c>
+      <c r="K154" t="n">
+        <v>1.799925441779615</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0.4912460266865761</v>
       </c>
     </row>
     <row r="155">
@@ -5554,7 +6946,16 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>7.285670912075997</v>
+        <v>7.102181184657598</v>
+      </c>
+      <c r="J155" t="n">
+        <v>1.938368227253711</v>
+      </c>
+      <c r="K155" t="n">
+        <v>6.805577643430621</v>
+      </c>
+      <c r="L155" t="n">
+        <v>1.857417479102244</v>
       </c>
     </row>
     <row r="156">
@@ -5587,7 +6988,16 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>7.644206411084259</v>
+        <v>7.451686961931681</v>
+      </c>
+      <c r="J156" t="n">
+        <v>2.033757358605808</v>
+      </c>
+      <c r="K156" t="n">
+        <v>7.230513941245556</v>
+      </c>
+      <c r="L156" t="n">
+        <v>1.973393542916363</v>
       </c>
     </row>
     <row r="157">
@@ -5620,7 +7030,16 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>-1.405180721718444</v>
+        <v>-1.369791224894707</v>
+      </c>
+      <c r="J157" t="n">
+        <v>-0.3738513168380751</v>
+      </c>
+      <c r="K157" t="n">
+        <v>-1.374665598234508</v>
+      </c>
+      <c r="L157" t="n">
+        <v>-0.3751816589067981</v>
       </c>
     </row>
     <row r="158">
@@ -5653,7 +7072,16 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.2223596776753166</v>
+        <v>0.2167595459732574</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0.05915926473069253</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0.2080012763780454</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0.0567689073084185</v>
       </c>
     </row>
     <row r="159">
@@ -5686,7 +7114,16 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>30.33416929863131</v>
+        <v>29.5702028056013</v>
+      </c>
+      <c r="J159" t="n">
+        <v>8.07047019803529</v>
+      </c>
+      <c r="K159" t="n">
+        <v>27.48368700281458</v>
+      </c>
+      <c r="L159" t="n">
+        <v>7.501006278060748</v>
       </c>
     </row>
     <row r="160">
@@ -5719,7 +7156,16 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.030017135844681</v>
+        <v>1.004076139363607</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0.2740382476429059</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0.9183121557173836</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0.2506310468660981</v>
       </c>
     </row>
     <row r="161">
@@ -5752,7 +7198,16 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.01049119731255592</v>
+        <v>0.01022697635632486</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0.002791205337424906</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0.009682198041081736</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0.002642521299421871</v>
       </c>
     </row>
     <row r="162">
@@ -5785,7 +7240,16 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>6.234917988928787</v>
+        <v>6.077891489094934</v>
+      </c>
+      <c r="J162" t="n">
+        <v>1.658813179338137</v>
+      </c>
+      <c r="K162" t="n">
+        <v>5.78206736801828</v>
+      </c>
+      <c r="L162" t="n">
+        <v>1.578075155026823</v>
       </c>
     </row>
     <row r="163">
@@ -5818,7 +7282,16 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>8.203497765778337</v>
+        <v>7.996892555759154</v>
+      </c>
+      <c r="J163" t="n">
+        <v>2.182558011943001</v>
+      </c>
+      <c r="K163" t="n">
+        <v>7.61087988167675</v>
+      </c>
+      <c r="L163" t="n">
+        <v>2.077205207881209</v>
       </c>
     </row>
     <row r="164">
@@ -5851,7 +7324,16 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.0254663060829514</v>
+        <v>0.02482493679549578</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0.006775364845932256</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0.02284779769878009</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0.006235752647046968</v>
       </c>
     </row>
     <row r="165">
@@ -5884,7 +7366,16 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.009153014554027694</v>
+        <v>0.008922495749947286</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0.002435178971055482</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0.008377651472914192</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0.002286476930380511</v>
       </c>
     </row>
     <row r="166">
@@ -5917,7 +7408,16 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3.111220183909269</v>
+        <v>3.032864058526512</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0.8277467408642227</v>
+      </c>
+      <c r="K166" t="n">
+        <v>2.906169159261908</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0.7931684386631845</v>
       </c>
     </row>
     <row r="167">
@@ -5950,7 +7450,16 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5.19159248604588</v>
+        <v>5.060842154109665</v>
+      </c>
+      <c r="J167" t="n">
+        <v>1.381234212366175</v>
+      </c>
+      <c r="K167" t="n">
+        <v>4.783100320701178</v>
+      </c>
+      <c r="L167" t="n">
+        <v>1.305431310235037</v>
       </c>
     </row>
     <row r="168">
@@ -5983,7 +7492,16 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.8937470246847</v>
+        <v>2.820867963966062</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0.7698875447505626</v>
+      </c>
+      <c r="K168" t="n">
+        <v>2.733773688332497</v>
+      </c>
+      <c r="L168" t="n">
+        <v>0.7461172730165112</v>
       </c>
     </row>
     <row r="169">
@@ -6016,7 +7534,16 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.4765087090924826</v>
+        <v>0.4645078303540606</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0.1267761545726148</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0.4439685822074215</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0.1211704645762613</v>
       </c>
     </row>
   </sheetData>
